--- a/questionnaire_templates/002_diy_beauty_practice_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/002_diy_beauty_practice_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your age group?</t>
+          <t>Age Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How often do you practice at-home beauty routines?</t>
+          <t>Practice Frequency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>practice_difficulties</t>
+          <t>practice_difficulties_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Which of the following are challenges you face with at-home beauty routines?</t>
+          <t>Practice Difficulties 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>strongly agree</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>word of mouth</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>online_reviews</t>
+          <t>online reviews</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>offline_ads</t>
+          <t>offline ads</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>use_it</t>
+          <t>use it</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>return_it</t>
+          <t>return it</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>share_it_with_friends</t>
+          <t>share it with friends</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>share_on_social_media</t>
+          <t>share on social media</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>purchase_it</t>
+          <t>purchase it</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>purchase_it_sometimes</t>
+          <t>purchase it sometimes</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>purchased_it</t>
+          <t>purchased it</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>purchased_it_sometimes</t>
+          <t>purchased it sometimes</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>highly_motivated</t>
+          <t>highly motivated</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>somewhat_motivated</t>
+          <t>somewhat motivated</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>somewhat_unmotivated</t>
+          <t>somewhat unmotivated</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>highly_unmotivated</t>
+          <t>highly unmotivated</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>purchase_in_store</t>
+          <t>purchase in store</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>purchase_online</t>
+          <t>purchase online</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>skin_type</t>
+          <t>skin type</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>product_availability</t>
+          <t>product availability</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>very_frequently</t>
+          <t>very frequently</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>somewhat_frequently</t>
+          <t>somewhat frequently</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>practice_difficulties_choices</t>
+          <t>practice_difficulties_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2343,14 +2343,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>product_effectiveness</t>
+          <t>product effectiveness</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>practice_difficulties_choices</t>
+          <t>practice_difficulties_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2360,14 +2360,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ingredient_safety</t>
+          <t>ingredient safety</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>practice_difficulties_choices</t>
+          <t>practice_difficulties_2_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2377,14 +2377,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>skin_type</t>
+          <t>skin type</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>practice_difficulties_choices</t>
+          <t>practice_difficulties_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>very_effective</t>
+          <t>very effective</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>somewhat_effective</t>
+          <t>somewhat effective</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>somewhat_ineffective</t>
+          <t>somewhat ineffective</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>very_ineffective</t>
+          <t>very ineffective</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>very_sensitive</t>
+          <t>very sensitive</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>somewhat_sensitive</t>
+          <t>somewhat sensitive</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>not_sensitive</t>
+          <t>not sensitive</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>highly_likely</t>
+          <t>highly likely</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>not_at_all_likely</t>
+          <t>not at all likely</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
